--- a/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
+++ b/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C58033A-C95A-4143-9378-15FE9BF8743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6107964A-3BCB-BD48-B06F-C0581EE6CEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1120" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>https://fairlightcycles.com/secan-3-0/?v=0b3b97fa6688</t>
+  </si>
+  <si>
+    <t>https://media.fairlightcycles.com/wp-content/uploads/2024/12/2560-x-1152-Banner-Master-Secan-3.0-Burnt-Orange.jpg</t>
   </si>
 </sst>
 </file>
@@ -809,6 +812,11 @@
         <v>117</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>

--- a/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
+++ b/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6107964A-3BCB-BD48-B06F-C0581EE6CEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274E7F50-DB5B-0A48-AA0D-4B5BB222C6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1120" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -353,9 +353,6 @@
     <t>steel</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>Trail - 650 x 47 Tyres (685mm)</t>
   </si>
   <si>
@@ -390,13 +387,22 @@
   </si>
   <si>
     <t>https://media.fairlightcycles.com/wp-content/uploads/2024/12/2560-x-1152-Banner-Master-Secan-3.0-Burnt-Orange.jpg</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>London, United Kingdom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -436,6 +442,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -457,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -467,6 +479,7 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -785,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -809,12 +822,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -822,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -1197,10 +1210,10 @@
     </row>
     <row r="16" spans="1:22" ht="22" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="8">
         <v>71.5</v>
@@ -1246,7 +1259,7 @@
         <v>104</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="8">
         <v>73.599999999999994</v>
@@ -1290,10 +1303,10 @@
     </row>
     <row r="18" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="8">
         <v>74.5</v>
@@ -1571,7 +1584,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="8">
         <v>756</v>
@@ -2040,7 +2053,7 @@
         <v>49</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -2069,7 +2082,7 @@
         <v>53</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -2168,11 +2181,19 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>106</v>
+      <c r="B76" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
+++ b/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274E7F50-DB5B-0A48-AA0D-4B5BB222C6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305EB53E-3819-0B40-A707-429E22DD57EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1120" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>London, United Kingdom</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -2089,6 +2092,9 @@
       <c r="A63" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="B63" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">

--- a/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
+++ b/data/gravel/Fairlight Secan 3.0 R 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305EB53E-3819-0B40-A707-429E22DD57EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7D1AB2-E96C-1044-922A-CD19A0728043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1120" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -779,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V77"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -2016,134 +2034,119 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="2">
-        <v>27.2</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="2">
-        <v>42</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="2">
-        <v>180</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="2">
-        <v>180</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B61" s="2">
+        <v>27.2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>121</v>
+        <v>48</v>
+      </c>
+      <c r="B63" s="2">
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B65" s="2">
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="2">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="2">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>74</v>
@@ -2151,54 +2154,99 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
+      </c>
+      <c r="B72" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B73" s="2">
-        <v>1245</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="2">
-        <v>2225</v>
+        <v>59</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="2">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B82" s="9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="9" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B83" s="9" t="s">
         <v>120</v>
       </c>
     </row>
